--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
@@ -127,31 +127,31 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>A0377F18A101A3401D66526588E03545</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>ver nota</t>
-  </si>
-  <si>
     <t>Subdirección Jurídica</t>
   </si>
   <si>
-    <t>10/10/2022</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo  por alguna recomendación por  casos especiales</t>
+    <t>3B5C9DED715914A4A0212F0FCA304AD4</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>08/10/2023</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t>Del periodo del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por alguna recomendación por  casos especiales.</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -559,7 +559,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="159.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="157.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -732,19 +732,19 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>38</v>
@@ -759,10 +759,10 @@
         <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>44</v>
